--- a/inst/resources/outputs_schema_data_analytics_mortality_deaths_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_mortality_deaths_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SaeedRAHMAN\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58473C9E-77F6-465D-81D6-17154AD94530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123DA00D-9528-4472-9778-A43D22447816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24150" yWindow="75" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
   <si>
     <t>output_title</t>
   </si>
@@ -76,9 +76,6 @@
     <t>survey_design</t>
   </si>
   <si>
-    <t>age_pyramid_deaths_overall_weighted</t>
-  </si>
-  <si>
     <t>weighted</t>
   </si>
   <si>
@@ -94,10 +91,37 @@
     <t>table</t>
   </si>
   <si>
-    <t>basic_death_demo_table_strata</t>
-  </si>
-  <si>
     <t>sex,age_years</t>
+  </si>
+  <si>
+    <t>unweighted</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>age_pyramid_deaths_overall_weighted1</t>
+  </si>
+  <si>
+    <t>age_pyramid_deaths_overall_weighted2</t>
+  </si>
+  <si>
+    <t>age_pyramid_deaths_overall_weighted3</t>
+  </si>
+  <si>
+    <t>age_pyramid_deaths_overall_weighted4</t>
+  </si>
+  <si>
+    <t>basic_death_demo_table_strata1</t>
+  </si>
+  <si>
+    <t>basic_death_demo_table_strata2</t>
+  </si>
+  <si>
+    <t>basic_death_demo_table_strata3</t>
+  </si>
+  <si>
+    <t>basic_death_demo_table_strata4</t>
   </si>
 </sst>
 </file>
@@ -448,12 +472,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="14" width="16.85546875" customWidth="1"/>
+    <col min="3" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="46.42578125" customWidth="1"/>
+    <col min="8" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" customWidth="1"/>
+    <col min="11" max="14" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -502,13 +531,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
@@ -520,42 +549,204 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="K3" t="s">
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{E6023C82-803B-4C33-B92C-C1E4199320D7}"/>
-    <hyperlink ref="G3" r:id="rId2" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{99016C6F-F5ED-4BC8-9201-FD59130CD9DE}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{E6023C82-803B-4C33-B92C-C1E4199320D7}"/>
+    <hyperlink ref="G9" r:id="rId2" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{99016C6F-F5ED-4BC8-9201-FD59130CD9DE}"/>
+    <hyperlink ref="G2" r:id="rId3" xr:uid="{EC68F78F-C5CB-466A-8DA7-24D084AD0853}"/>
+    <hyperlink ref="G3" r:id="rId4" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{20744283-3DF6-443E-B9C7-BA5AFCAAA3A0}"/>
+    <hyperlink ref="G4" r:id="rId5" xr:uid="{0FB4AD86-DBC6-4811-BA63-3B4971B72466}"/>
+    <hyperlink ref="G5" r:id="rId6" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{A848612C-95F8-4DD4-8460-F32096190005}"/>
+    <hyperlink ref="G6" r:id="rId7" xr:uid="{99F025D2-1BA7-4E17-A8A8-B76699B7B3E8}"/>
+    <hyperlink ref="G7" r:id="rId8" display="variable=@variable_map$age_cat,stat_type=&quot;percentage&quot;,disaggregation=@variable_map$sex,variable_label=@variable_label$age_cat,disaggregation_wide=TRUE" xr:uid="{4D3D55A1-C833-4961-9138-50320FC3BD42}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inst/resources/outputs_schema_data_analytics_mortality_deaths_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_mortality_deaths_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123DA00D-9528-4472-9778-A43D22447816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EE2165-7491-4F44-95BD-E0F92D21CEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24150" yWindow="75" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t>output_title</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>basic_death_demo_table_strata4</t>
+  </si>
+  <si>
+    <t>variable=c(@variable_map$sex, @variable_map$age_years, @variable_map$age_months_cat),stat_type=c("percentage","mean","percentage"),variable_label=c(@variable_label$sex, @variable_label$age_years,@variable_label$age_months_cat), show_ci=TRUE,disaggregation_wide=TRUE,disaggregation=@variable_map$stratum,weighted_result=TRUE</t>
   </si>
 </sst>
 </file>
@@ -725,7 +728,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
